--- a/data/trans_dic/P36$pan-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,92; 78,4</t>
+          <t>71,64; 78,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,71; 85,42</t>
+          <t>79,2; 85,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,65; 83,34</t>
+          <t>77,4; 83,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,65; 83,61</t>
+          <t>77,68; 83,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,08; 85,86</t>
+          <t>80,24; 85,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,25; 87,75</t>
+          <t>82,23; 87,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,63; 79,98</t>
+          <t>75,57; 79,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,74; 84,79</t>
+          <t>80,75; 84,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80,85; 85,12</t>
+          <t>80,89; 84,97</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,73; 83,93</t>
+          <t>78,68; 83,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,42; 82,4</t>
+          <t>77,05; 82,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,46; 87,2</t>
+          <t>82,62; 87,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,5; 81,61</t>
+          <t>76,22; 81,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,87; 88,35</t>
+          <t>83,52; 88,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,43; 87,75</t>
+          <t>83,54; 87,74</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,02; 81,82</t>
+          <t>78,24; 81,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,33; 84,75</t>
+          <t>81,33; 84,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,54; 86,87</t>
+          <t>83,71; 86,83</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,83; 78,09</t>
+          <t>70,59; 77,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,78; 81,89</t>
+          <t>75,66; 82,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,94; 88,02</t>
+          <t>82,88; 87,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72,24; 78,74</t>
+          <t>72,24; 78,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,6; 83,51</t>
+          <t>77,9; 83,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,48; 91,85</t>
+          <t>87,28; 91,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,65; 77,44</t>
+          <t>72,75; 77,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,63; 82,1</t>
+          <t>77,8; 82,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,8; 89,44</t>
+          <t>85,99; 89,44</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,56; 76,58</t>
+          <t>71,1; 76,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,75; 82,1</t>
+          <t>76,55; 81,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>82,97; 87,83</t>
+          <t>83,03; 87,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,75; 79,88</t>
+          <t>74,82; 79,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,61; 83,36</t>
+          <t>78,78; 83,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,59; 91,37</t>
+          <t>87,38; 91,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,76; 77,57</t>
+          <t>73,5; 77,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,45; 82,06</t>
+          <t>78,35; 81,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,17; 89,22</t>
+          <t>86,26; 89,11</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,98; 77,87</t>
+          <t>74,85; 77,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,62; 81,44</t>
+          <t>78,76; 81,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,13; 85,69</t>
+          <t>83,14; 85,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,77; 79,51</t>
+          <t>76,64; 79,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,58; 84,22</t>
+          <t>81,57; 84,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,45; 88,67</t>
+          <t>86,5; 88,82</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,3; 78,34</t>
+          <t>76,29; 78,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>80,67; 82,55</t>
+          <t>80,52; 82,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85,23; 86,92</t>
+          <t>85,21; 86,93</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ...</t>
+          <t>Población que desayuna, al menos, pan, tostadas, galletas, cereales, bollería, ... (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>498405; 543324</t>
+          <t>496491; 543189</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>559171; 599221</t>
+          <t>555535; 598334</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>522606; 560868</t>
+          <t>520882; 564515</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>534533; 575500</t>
+          <t>534682; 574156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>557413; 597687</t>
+          <t>558536; 596701</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>552435; 589360</t>
+          <t>552318; 589061</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1044676; 1104857</t>
+          <t>1043954; 1103589</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1128356; 1185043</t>
+          <t>1128605; 1184969</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1087168; 1144575</t>
+          <t>1087666; 1142592</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>754877; 804823</t>
+          <t>754407; 803858</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>788053; 838751</t>
+          <t>784324; 838746</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>842212; 890632</t>
+          <t>843841; 890154</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>740089; 789490</t>
+          <t>737347; 787958</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>863933; 910124</t>
+          <t>860401; 907654</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>869330; 914330</t>
+          <t>870463; 914268</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1502953; 1575985</t>
+          <t>1507176; 1577340</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1665776; 1735678</t>
+          <t>1665790; 1736948</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1723581; 1792297</t>
+          <t>1727212; 1791564</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>479864; 529044</t>
+          <t>478253; 526618</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>572599; 618729</t>
+          <t>571688; 619959</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>629045; 667583</t>
+          <t>628597; 667080</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>494030; 538485</t>
+          <t>494008; 536742</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>602310; 648159</t>
+          <t>604673; 649310</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>686699; 721036</t>
+          <t>685187; 719303</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>988999; 1054230</t>
+          <t>990302; 1057920</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1189076; 1257596</t>
+          <t>1191767; 1259148</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1324310; 1380470</t>
+          <t>1327227; 1380555</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>663570; 720182</t>
+          <t>668660; 719003</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>725918; 776552</t>
+          <t>724027; 775490</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>777902; 823436</t>
+          <t>778443; 822861</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>774053; 827186</t>
+          <t>774797; 826996</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>825203; 875095</t>
+          <t>827042; 879328</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>913233; 952727</t>
+          <t>911101; 953240</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1457512; 1532888</t>
+          <t>1452350; 1528323</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1565520; 1637542</t>
+          <t>1563491; 1635142</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1706368; 1766806</t>
+          <t>1708116; 1764598</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2451660; 2546062</t>
+          <t>2447433; 2549606</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2689402; 2785872</t>
+          <t>2694410; 2788728</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2818298; 2905288</t>
+          <t>2818906; 2905461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2591023; 2683720</t>
+          <t>2586715; 2685599</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2897809; 2991591</t>
+          <t>2897471; 2987930</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3061402; 3139965</t>
+          <t>3063207; 3145274</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5070013; 5205592</t>
+          <t>5069578; 5206523</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5625395; 5756348</t>
+          <t>5614404; 5748032</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5907625; 6024899</t>
+          <t>5906603; 6025465</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$pan-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P36$pan-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>71,64; 78,38</t>
+          <t>72,08; 78,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>79,2; 85,3</t>
+          <t>79,62; 85,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>77,4; 83,88</t>
+          <t>77,54; 84,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77,68; 83,41</t>
+          <t>77,29; 83,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,24; 85,72</t>
+          <t>80,16; 85,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,23; 87,7</t>
+          <t>82,3; 87,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,57; 79,89</t>
+          <t>75,63; 80,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>80,75; 84,79</t>
+          <t>80,82; 84,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>80,89; 84,97</t>
+          <t>80,94; 85,19</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>78,68; 83,83</t>
+          <t>78,38; 83,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,05; 82,4</t>
+          <t>77,1; 82,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82,62; 87,16</t>
+          <t>82,47; 87,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76,22; 81,45</t>
+          <t>75,95; 81,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,52; 88,11</t>
+          <t>83,62; 88,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,54; 87,74</t>
+          <t>83,56; 87,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,24; 81,89</t>
+          <t>78,16; 81,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,33; 84,81</t>
+          <t>81,29; 84,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>83,71; 86,83</t>
+          <t>83,47; 86,98</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>70,59; 77,73</t>
+          <t>71,21; 78,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>75,66; 82,05</t>
+          <t>75,72; 81,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,88; 87,95</t>
+          <t>82,78; 88,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72,24; 78,49</t>
+          <t>72,18; 78,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77,9; 83,65</t>
+          <t>77,52; 83,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,28; 91,63</t>
+          <t>87,15; 91,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,75; 77,71</t>
+          <t>72,64; 77,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>77,8; 82,2</t>
+          <t>77,43; 81,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85,99; 89,44</t>
+          <t>85,93; 89,45</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,1; 76,45</t>
+          <t>70,44; 76,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>76,55; 81,99</t>
+          <t>76,48; 81,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83,03; 87,77</t>
+          <t>82,9; 87,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74,82; 79,86</t>
+          <t>74,79; 79,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,78; 83,76</t>
+          <t>78,6; 83,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,38; 91,42</t>
+          <t>87,52; 91,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,5; 77,34</t>
+          <t>73,71; 77,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>78,35; 81,94</t>
+          <t>78,61; 82,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86,26; 89,11</t>
+          <t>86,13; 89,12</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>74,85; 77,97</t>
+          <t>74,97; 77,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,76; 81,52</t>
+          <t>78,81; 81,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,14; 85,7</t>
+          <t>83,23; 85,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,64; 79,57</t>
+          <t>76,73; 79,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>81,57; 84,12</t>
+          <t>81,59; 84,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,5; 88,82</t>
+          <t>86,42; 88,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,29; 78,35</t>
+          <t>76,21; 78,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>80,52; 82,43</t>
+          <t>80,55; 82,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>85,21; 86,93</t>
+          <t>85,25; 86,85</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>496491; 543189</t>
+          <t>499565; 543871</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>555535; 598334</t>
+          <t>558486; 599806</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>520882; 564515</t>
+          <t>521825; 566872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>534682; 574156</t>
+          <t>532008; 574339</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>558536; 596701</t>
+          <t>557996; 598424</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>552318; 589061</t>
+          <t>552784; 590758</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1043954; 1103589</t>
+          <t>1044671; 1105621</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1128605; 1184969</t>
+          <t>1129471; 1184352</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1087666; 1142592</t>
+          <t>1088352; 1145572</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>754407; 803858</t>
+          <t>751555; 803435</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>784324; 838746</t>
+          <t>784820; 838901</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>843841; 890154</t>
+          <t>842239; 890473</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>737347; 787958</t>
+          <t>734724; 787182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>860401; 907654</t>
+          <t>861361; 908894</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>870463; 914268</t>
+          <t>870681; 915647</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1507176; 1577340</t>
+          <t>1505639; 1577190</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1665790; 1736948</t>
+          <t>1664847; 1734499</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1727212; 1791564</t>
+          <t>1722212; 1794667</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>478253; 526618</t>
+          <t>482404; 531156</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>571688; 619959</t>
+          <t>572144; 617872</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>628597; 667080</t>
+          <t>627829; 667551</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>494008; 536742</t>
+          <t>493602; 539497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>604673; 649310</t>
+          <t>601698; 647430</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>685187; 719303</t>
+          <t>684152; 720367</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>990302; 1057920</t>
+          <t>988846; 1055041</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1191767; 1259148</t>
+          <t>1186028; 1252533</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1327227; 1380555</t>
+          <t>1326354; 1380686</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>668660; 719003</t>
+          <t>662482; 716223</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>724027; 775490</t>
+          <t>723371; 774080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>778443; 822861</t>
+          <t>777203; 821939</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>774797; 826996</t>
+          <t>774536; 826900</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>827042; 879328</t>
+          <t>825138; 878299</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>911101; 953240</t>
+          <t>912547; 952365</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1452350; 1528323</t>
+          <t>1456610; 1530642</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1563491; 1635142</t>
+          <t>1568766; 1639273</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1708116; 1764598</t>
+          <t>1705491; 1764833</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2447433; 2549606</t>
+          <t>2451542; 2544753</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2694410; 2788728</t>
+          <t>2695955; 2793756</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2818906; 2905461</t>
+          <t>2821863; 2902886</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2586715; 2685599</t>
+          <t>2589879; 2683530</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2897471; 2987930</t>
+          <t>2898251; 2988337</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3063207; 3145274</t>
+          <t>3060392; 3139268</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5069578; 5206523</t>
+          <t>5064353; 5203467</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5614404; 5748032</t>
+          <t>5616549; 5749723</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5906603; 6025465</t>
+          <t>5909064; 6020041</t>
         </is>
       </c>
     </row>
